--- a/data/Неделя_12.10-18.10_2026.xlsx
+++ b/data/Неделя_12.10-18.10_2026.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s.kulikova\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22ED3940-AB0E-439D-AFAD-3BC5473FA7F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11400" windowHeight="5892"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист_1" sheetId="1" r:id="rId1"/>
@@ -405,7 +411,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -500,7 +506,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -513,14 +519,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -558,7 +567,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -630,7 +639,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -803,7 +812,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
@@ -1880,7 +1889,7 @@
         <v>35</v>
       </c>
       <c r="L21" s="5" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="M21" s="5"/>
       <c r="N21" s="5" t="s">
@@ -1926,7 +1935,7 @@
         <v>35</v>
       </c>
       <c r="L22" s="5" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="M22" s="5"/>
       <c r="N22" s="5" t="s">
@@ -1972,7 +1981,7 @@
         <v>35</v>
       </c>
       <c r="L23" s="5" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="M23" s="5"/>
       <c r="N23" s="5" t="s">
@@ -2018,7 +2027,7 @@
         <v>35</v>
       </c>
       <c r="L24" s="5" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="M24" s="5"/>
       <c r="N24" s="5" t="s">
@@ -2064,7 +2073,7 @@
         <v>35</v>
       </c>
       <c r="L25" s="5" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="M25" s="5"/>
       <c r="N25" s="5" t="s">
@@ -2110,7 +2119,7 @@
         <v>35</v>
       </c>
       <c r="L26" s="5" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="M26" s="5"/>
       <c r="N26" s="5" t="s">
@@ -2306,7 +2315,7 @@
       <c r="R30" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1"/>
+  <autoFilter ref="A1:R1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="portrait" r:id="rId1"/>
 </worksheet>
